--- a/docs/验收清单_20260602.xlsx
+++ b/docs/验收清单_20260602.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/miko/Desktop/AI文档/6.热搜/Singularity-Radar/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C53149D-4374-C041-AA74-DC621B786849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14F41E67-194C-6443-BDA3-62F410DF0115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="23940" windowHeight="26560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,6 @@
     <t>Singularity Radar · 产品验收清单</t>
   </si>
   <si>
-    <t>版本 20260602 ｜ 生成日期 2026-06-02</t>
-  </si>
-  <si>
     <t>验收状态：通过 ｜ 不通过 ｜ 部分通过 ｜ 暂不修复 ｜ 跳过 ｜ 已修复待验证 ｜ 待确认</t>
   </si>
   <si>
@@ -1531,6 +1528,10 @@
   </si>
   <si>
     <t>夜间模式，刷新页面，底色为白色，日间模式刷新时，底色为黑色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>版本 20260602 ｜ 生成日期 2026-06-02 ｜ 测试环境：http://localhost:5173/admin ｜线上环境：https://sr.miko-ai.cn/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1702,7 +1703,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1778,6 +1779,9 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1791,8 +1795,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2264,27 +2268,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:10" ht="24" customHeight="1">
-      <c r="A2" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="A2" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -2292,82 +2296,82 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="22" customHeight="1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+    </row>
+    <row r="4" spans="1:10" ht="22" customHeight="1">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="4" spans="1:10" ht="22" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+    </row>
+    <row r="5" spans="1:10" ht="22" customHeight="1">
+      <c r="A5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-    </row>
-    <row r="5" spans="1:10" ht="22" customHeight="1">
-      <c r="A5" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="30" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="26" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2381,53 +2385,53 @@
     </row>
     <row r="8" spans="1:10" ht="32" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="D8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>19</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>20</v>
       </c>
       <c r="F8" s="9">
         <v>46171.39166666667</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="8"/>
       <c r="J8" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="32" customHeight="1">
       <c r="A9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="F9" s="9">
         <v>46171.39166666667</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="8"/>
@@ -2435,25 +2439,25 @@
     </row>
     <row r="10" spans="1:10" ht="32" customHeight="1">
       <c r="A10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G10" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="8"/>
@@ -2461,25 +2465,25 @@
     </row>
     <row r="11" spans="1:10" ht="32" customHeight="1">
       <c r="A11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="D11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="F11" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="8"/>
@@ -2487,55 +2491,55 @@
     </row>
     <row r="12" spans="1:10" ht="32" customHeight="1">
       <c r="A12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="F12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>36</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="32" customHeight="1">
       <c r="A13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="8" t="s">
+      <c r="D13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="F13" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="8"/>
@@ -2543,25 +2547,25 @@
     </row>
     <row r="14" spans="1:10" ht="32" customHeight="1">
       <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>44</v>
-      </c>
       <c r="F14" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="8"/>
@@ -2569,25 +2573,25 @@
     </row>
     <row r="15" spans="1:10" ht="32" customHeight="1">
       <c r="A15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="F15" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="8"/>
@@ -2595,25 +2599,25 @@
     </row>
     <row r="16" spans="1:10" ht="32" customHeight="1">
       <c r="A16" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="F16" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="8"/>
@@ -2621,7 +2625,7 @@
     </row>
     <row r="17" spans="1:10" ht="26" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2635,25 +2639,25 @@
     </row>
     <row r="18" spans="1:10" ht="32" customHeight="1">
       <c r="A18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="F18" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="8"/>
@@ -2661,25 +2665,25 @@
     </row>
     <row r="19" spans="1:10" ht="32" customHeight="1">
       <c r="A19" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>58</v>
-      </c>
       <c r="F19" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="8"/>
@@ -2687,25 +2691,25 @@
     </row>
     <row r="20" spans="1:10" ht="32" customHeight="1">
       <c r="A20" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="D20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="F20" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="8"/>
@@ -2713,25 +2717,25 @@
     </row>
     <row r="21" spans="1:10" ht="32" customHeight="1">
       <c r="A21" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="8" t="s">
+      <c r="D21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="F21" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="8"/>
@@ -2739,57 +2743,57 @@
     </row>
     <row r="22" spans="1:10" ht="32" customHeight="1">
       <c r="A22" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="32" customHeight="1">
       <c r="A23" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" s="8" t="s">
+      <c r="D23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>73</v>
-      </c>
       <c r="F23" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="8"/>
@@ -2797,25 +2801,25 @@
     </row>
     <row r="24" spans="1:10" ht="32" customHeight="1">
       <c r="A24" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="8"/>
@@ -2823,57 +2827,57 @@
     </row>
     <row r="25" spans="1:10" ht="32" customHeight="1">
       <c r="A25" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>79</v>
       </c>
       <c r="F25" s="9">
         <v>46171.39166666667</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="J25" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="32" customHeight="1">
       <c r="A26" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="F26" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="8"/>
@@ -2881,25 +2885,25 @@
     </row>
     <row r="27" spans="1:10" ht="32" customHeight="1">
       <c r="A27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="8" t="s">
+      <c r="D27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>87</v>
-      </c>
       <c r="F27" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="8"/>
@@ -2907,53 +2911,53 @@
     </row>
     <row r="28" spans="1:10" ht="32" customHeight="1">
       <c r="A28" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B28" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="F28" s="9">
         <v>46171.39166666667</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="32" customHeight="1">
       <c r="A29" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" s="8" t="s">
+      <c r="D29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>94</v>
-      </c>
       <c r="F29" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="8"/>
@@ -2961,25 +2965,25 @@
     </row>
     <row r="30" spans="1:10" ht="32" customHeight="1">
       <c r="A30" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="8" t="s">
+      <c r="D30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D30" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>97</v>
-      </c>
       <c r="F30" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H30" s="6"/>
       <c r="I30" s="8"/>
@@ -2987,39 +2991,39 @@
     </row>
     <row r="31" spans="1:10" ht="32" customHeight="1">
       <c r="A31" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" s="17" t="s">
+      <c r="D31" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>100</v>
       </c>
       <c r="F31" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H31" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I31" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="J31" s="17" t="s">
         <v>101</v>
-      </c>
-      <c r="J31" s="17" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="26" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -3033,55 +3037,55 @@
     </row>
     <row r="33" spans="1:10" ht="32" customHeight="1">
       <c r="A33" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="C33" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="D33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>106</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="F33" s="9">
         <v>46171.39166666667</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I33" s="8"/>
       <c r="J33" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="32" customHeight="1">
       <c r="A34" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="8" t="s">
+      <c r="D34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>112</v>
-      </c>
       <c r="F34" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="8"/>
@@ -3089,121 +3093,121 @@
     </row>
     <row r="35" spans="1:10" ht="32" customHeight="1">
       <c r="A35" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B35" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C35" s="8" t="s">
+      <c r="D35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>115</v>
       </c>
       <c r="F35" s="9">
         <v>46171.451388888891</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I35" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="J35" s="8" t="s">
         <v>116</v>
-      </c>
-      <c r="J35" s="8" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="32" customHeight="1">
       <c r="A36" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="8" t="s">
+      <c r="D36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>119</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>120</v>
       </c>
       <c r="F36" s="9">
         <v>46171.39166666667</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I36" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="J36" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="32" customHeight="1">
       <c r="A37" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B37" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C37" s="12" t="s">
+      <c r="D37" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="E37" s="12" t="s">
         <v>125</v>
-      </c>
-      <c r="E37" s="12" t="s">
-        <v>126</v>
       </c>
       <c r="F37" s="13">
         <v>46171.39166666667</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I37" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="J37" s="12" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="32" customHeight="1">
       <c r="A38" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B38" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="8" t="s">
+      <c r="D38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>131</v>
-      </c>
       <c r="F38" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="8"/>
@@ -3211,39 +3215,39 @@
     </row>
     <row r="39" spans="1:10" ht="32" customHeight="1">
       <c r="A39" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B39" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C39" s="8" t="s">
+      <c r="D39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>134</v>
       </c>
       <c r="F39" s="9">
         <v>46171.451388888891</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H39" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="I39" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="I39" s="8" t="s">
+      <c r="J39" s="8" t="s">
         <v>136</v>
-      </c>
-      <c r="J39" s="8" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="26" customHeight="1">
       <c r="A40" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3257,57 +3261,57 @@
     </row>
     <row r="41" spans="1:10" ht="32" customHeight="1">
       <c r="A41" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="B41" s="7" t="s">
+      <c r="C41" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="D41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>142</v>
       </c>
       <c r="F41" s="9">
         <v>46171.451388888891</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I41" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="J41" s="8" t="s">
         <v>143</v>
-      </c>
-      <c r="J41" s="8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="32" customHeight="1">
       <c r="A42" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" s="8" t="s">
+      <c r="D42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D42" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>147</v>
-      </c>
       <c r="F42" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="8"/>
@@ -3315,81 +3319,81 @@
     </row>
     <row r="43" spans="1:10" ht="32" customHeight="1">
       <c r="A43" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="B43" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C43" s="8" t="s">
+      <c r="D43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>149</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>150</v>
       </c>
       <c r="F43" s="9">
         <v>46171.39166666667</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="32" customHeight="1">
       <c r="A44" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="B44" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C44" s="12" t="s">
+      <c r="D44" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="F44" s="13">
         <v>46171.39166666667</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="32" customHeight="1">
       <c r="A45" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C45" s="8" t="s">
+      <c r="D45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>158</v>
-      </c>
       <c r="F45" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="8"/>
@@ -3397,25 +3401,25 @@
     </row>
     <row r="46" spans="1:10" ht="32" customHeight="1">
       <c r="A46" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B46" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C46" s="8" t="s">
+      <c r="D46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>161</v>
-      </c>
       <c r="F46" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="8"/>
@@ -3423,25 +3427,25 @@
     </row>
     <row r="47" spans="1:10" ht="32" customHeight="1">
       <c r="A47" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B47" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C47" s="8" t="s">
+      <c r="D47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D47" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>164</v>
-      </c>
       <c r="F47" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="8"/>
@@ -3449,25 +3453,25 @@
     </row>
     <row r="48" spans="1:10" ht="32" customHeight="1">
       <c r="A48" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="B48" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C48" s="8" t="s">
+      <c r="D48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>167</v>
-      </c>
       <c r="F48" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="8"/>
@@ -3475,25 +3479,25 @@
     </row>
     <row r="49" spans="1:10" ht="32" customHeight="1">
       <c r="A49" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B49" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C49" s="8" t="s">
+      <c r="D49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="D49" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>170</v>
-      </c>
       <c r="F49" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="8"/>
@@ -3501,25 +3505,25 @@
     </row>
     <row r="50" spans="1:10" ht="32" customHeight="1">
       <c r="A50" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B50" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="C50" s="8" t="s">
+      <c r="D50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>173</v>
-      </c>
       <c r="F50" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="8"/>
@@ -3527,7 +3531,7 @@
     </row>
     <row r="51" spans="1:10" ht="26" customHeight="1">
       <c r="A51" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -3541,25 +3545,25 @@
     </row>
     <row r="52" spans="1:10" ht="32" customHeight="1">
       <c r="A52" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="7" t="s">
+      <c r="C52" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="D52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="D52" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="F52" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H52" s="6"/>
       <c r="I52" s="8"/>
@@ -3567,25 +3571,25 @@
     </row>
     <row r="53" spans="1:10" ht="32" customHeight="1">
       <c r="A53" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C53" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="B53" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C53" s="12" t="s">
+      <c r="D53" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E53" s="12" t="s">
         <v>180</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>181</v>
       </c>
       <c r="F53" s="13">
         <v>46170</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H53" s="10"/>
       <c r="I53" s="12"/>
@@ -3593,25 +3597,25 @@
     </row>
     <row r="54" spans="1:10" ht="32" customHeight="1">
       <c r="A54" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="B54" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C54" s="12" t="s">
+      <c r="D54" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E54" s="12" t="s">
         <v>183</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>184</v>
       </c>
       <c r="F54" s="13">
         <v>46170</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H54" s="10"/>
       <c r="I54" s="12"/>
@@ -3619,25 +3623,25 @@
     </row>
     <row r="55" spans="1:10" ht="32" customHeight="1">
       <c r="A55" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C55" s="12" t="s">
+      <c r="D55" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E55" s="12" t="s">
         <v>186</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>187</v>
       </c>
       <c r="F55" s="13">
         <v>46170</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H55" s="10"/>
       <c r="I55" s="12"/>
@@ -3645,25 +3649,25 @@
     </row>
     <row r="56" spans="1:10" ht="32" customHeight="1">
       <c r="A56" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C56" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="B56" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C56" s="12" t="s">
+      <c r="D56" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E56" s="12" t="s">
         <v>189</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>190</v>
       </c>
       <c r="F56" s="13">
         <v>46170</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H56" s="10"/>
       <c r="I56" s="12"/>
@@ -3671,25 +3675,25 @@
     </row>
     <row r="57" spans="1:10" ht="32" customHeight="1">
       <c r="A57" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C57" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B57" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C57" s="12" t="s">
+      <c r="D57" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E57" s="12" t="s">
         <v>192</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>193</v>
       </c>
       <c r="F57" s="13">
         <v>46170</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H57" s="10"/>
       <c r="I57" s="12"/>
@@ -3697,25 +3701,25 @@
     </row>
     <row r="58" spans="1:10" ht="32" customHeight="1">
       <c r="A58" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="C58" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="B58" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="C58" s="12" t="s">
+      <c r="D58" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E58" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="F58" s="13">
         <v>46170</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="12"/>
@@ -3723,7 +3727,7 @@
     </row>
     <row r="59" spans="1:10" ht="26" customHeight="1">
       <c r="A59" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -3737,25 +3741,25 @@
     </row>
     <row r="60" spans="1:10" ht="32" customHeight="1">
       <c r="A60" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="B60" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="C60" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C60" s="12" t="s">
+      <c r="D60" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E60" s="12" t="s">
         <v>200</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>201</v>
       </c>
       <c r="F60" s="13">
         <v>46170</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H60" s="10"/>
       <c r="I60" s="12"/>
@@ -3763,25 +3767,25 @@
     </row>
     <row r="61" spans="1:10" ht="32" customHeight="1">
       <c r="A61" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C61" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="B61" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C61" s="12" t="s">
+      <c r="D61" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E61" s="12" t="s">
         <v>203</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>204</v>
       </c>
       <c r="F61" s="13">
         <v>46170</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H61" s="10"/>
       <c r="I61" s="12"/>
@@ -3789,25 +3793,25 @@
     </row>
     <row r="62" spans="1:10" ht="32" customHeight="1">
       <c r="A62" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="B62" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C62" s="12" t="s">
+      <c r="D62" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E62" s="12" t="s">
         <v>206</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>207</v>
       </c>
       <c r="F62" s="13">
         <v>46170</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H62" s="10"/>
       <c r="I62" s="12"/>
@@ -3815,25 +3819,25 @@
     </row>
     <row r="63" spans="1:10" ht="32" customHeight="1">
       <c r="A63" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C63" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B63" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C63" s="12" t="s">
+      <c r="D63" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E63" s="12" t="s">
         <v>209</v>
-      </c>
-      <c r="D63" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>210</v>
       </c>
       <c r="F63" s="13">
         <v>46170</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H63" s="10"/>
       <c r="I63" s="12"/>
@@ -3841,25 +3845,25 @@
     </row>
     <row r="64" spans="1:10" ht="32" customHeight="1">
       <c r="A64" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C64" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="B64" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C64" s="12" t="s">
+      <c r="D64" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="D64" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>213</v>
       </c>
       <c r="F64" s="13">
         <v>46170</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H64" s="10"/>
       <c r="I64" s="12"/>
@@ -3867,25 +3871,25 @@
     </row>
     <row r="65" spans="1:10" ht="32" customHeight="1">
       <c r="A65" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C65" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B65" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C65" s="12" t="s">
+      <c r="D65" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" s="12" t="s">
         <v>215</v>
-      </c>
-      <c r="D65" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>216</v>
       </c>
       <c r="F65" s="13">
         <v>46170</v>
       </c>
       <c r="G65" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H65" s="10"/>
       <c r="I65" s="12"/>
@@ -3893,25 +3897,25 @@
     </row>
     <row r="66" spans="1:10" ht="32" customHeight="1">
       <c r="A66" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C66" s="12" t="s">
+      <c r="D66" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" s="12" t="s">
         <v>218</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>219</v>
       </c>
       <c r="F66" s="13">
         <v>46170</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H66" s="10"/>
       <c r="I66" s="12"/>
@@ -3919,25 +3923,25 @@
     </row>
     <row r="67" spans="1:10" ht="32" customHeight="1">
       <c r="A67" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C67" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B67" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C67" s="12" t="s">
+      <c r="D67" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" s="12" t="s">
         <v>221</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="F67" s="13">
         <v>46170</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H67" s="10"/>
       <c r="I67" s="12"/>
@@ -3945,35 +3949,35 @@
     </row>
     <row r="68" spans="1:10" ht="32" customHeight="1">
       <c r="A68" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="B68" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="C68" s="12" t="s">
+      <c r="D68" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D68" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E68" s="12" t="s">
+      <c r="F68" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F68" s="10" t="s">
-        <v>226</v>
-      </c>
       <c r="G68" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H68" s="10"/>
       <c r="I68" s="12"/>
       <c r="J68" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="26" customHeight="1">
       <c r="A69" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -3987,25 +3991,25 @@
     </row>
     <row r="70" spans="1:10" ht="32" customHeight="1">
       <c r="A70" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B70" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="C70" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="D70" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="D70" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E70" s="8" t="s">
+      <c r="F70" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="H70" s="6"/>
       <c r="I70" s="8"/>
@@ -4013,117 +4017,117 @@
     </row>
     <row r="71" spans="1:10" ht="32" customHeight="1">
       <c r="A71" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C71" s="8" t="s">
+      <c r="D71" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E71" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E71" s="8" t="s">
-        <v>236</v>
       </c>
       <c r="F71" s="9">
         <v>46171.451388888891</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I71" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="J71" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="J71" s="8" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="32" customHeight="1">
       <c r="A72" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="B72" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C72" s="8" t="s">
+      <c r="D72" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E72" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D72" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E72" s="8" t="s">
-        <v>241</v>
-      </c>
       <c r="F72" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H72" s="6"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="32" customHeight="1">
       <c r="A73" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C73" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="B73" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C73" s="8" t="s">
+      <c r="D73" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>245</v>
       </c>
       <c r="F73" s="9">
         <v>46171.477777777778</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I73" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="J73" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="J73" s="8" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="32" customHeight="1">
       <c r="A74" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="B74" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C74" s="8" t="s">
+      <c r="D74" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E74" s="8" t="s">
         <v>249</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E74" s="8" t="s">
-        <v>250</v>
-      </c>
       <c r="F74" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H74" s="6"/>
       <c r="I74" s="8"/>
@@ -4131,25 +4135,25 @@
     </row>
     <row r="75" spans="1:10" ht="32" customHeight="1">
       <c r="A75" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C75" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="B75" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="C75" s="12" t="s">
+      <c r="D75" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E75" s="12" t="s">
         <v>252</v>
-      </c>
-      <c r="D75" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E75" s="12" t="s">
-        <v>253</v>
       </c>
       <c r="F75" s="13">
         <v>46170</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H75" s="10"/>
       <c r="I75" s="12"/>
@@ -4157,25 +4161,25 @@
     </row>
     <row r="76" spans="1:10" ht="32" customHeight="1">
       <c r="A76" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="B76" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C76" s="8" t="s">
+      <c r="D76" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E76" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D76" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E76" s="8" t="s">
-        <v>256</v>
-      </c>
       <c r="F76" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H76" s="6"/>
       <c r="I76" s="8"/>
@@ -4183,25 +4187,25 @@
     </row>
     <row r="77" spans="1:10" ht="32" customHeight="1">
       <c r="A77" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C77" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B77" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C77" s="8" t="s">
+      <c r="D77" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E77" s="8" t="s">
         <v>258</v>
       </c>
-      <c r="D77" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>259</v>
-      </c>
       <c r="F77" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G77" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H77" s="6"/>
       <c r="I77" s="8"/>
@@ -4209,25 +4213,25 @@
     </row>
     <row r="78" spans="1:10" ht="32" customHeight="1">
       <c r="A78" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C78" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="B78" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C78" s="8" t="s">
+      <c r="D78" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="D78" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>262</v>
-      </c>
       <c r="F78" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H78" s="6"/>
       <c r="I78" s="8"/>
@@ -4235,25 +4239,25 @@
     </row>
     <row r="79" spans="1:10" ht="32" customHeight="1">
       <c r="A79" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="B79" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C79" s="8" t="s">
+      <c r="D79" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E79" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="D79" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>265</v>
-      </c>
       <c r="F79" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H79" s="6"/>
       <c r="I79" s="8"/>
@@ -4261,25 +4265,25 @@
     </row>
     <row r="80" spans="1:10" ht="32" customHeight="1">
       <c r="A80" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="B80" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C80" s="8" t="s">
+      <c r="D80" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="D80" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>268</v>
-      </c>
       <c r="F80" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H80" s="6"/>
       <c r="I80" s="8"/>
@@ -4287,25 +4291,25 @@
     </row>
     <row r="81" spans="1:10" ht="32" customHeight="1">
       <c r="A81" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="B81" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="C81" s="8" t="s">
+      <c r="D81" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E81" s="8" t="s">
         <v>270</v>
       </c>
-      <c r="D81" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>271</v>
-      </c>
       <c r="F81" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H81" s="6"/>
       <c r="I81" s="8"/>
@@ -4313,7 +4317,7 @@
     </row>
     <row r="82" spans="1:10" ht="26" customHeight="1">
       <c r="A82" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -4327,25 +4331,25 @@
     </row>
     <row r="83" spans="1:10" ht="32" customHeight="1">
       <c r="A83" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B83" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="B83" s="7" t="s">
+      <c r="C83" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="D83" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="8" t="s">
         <v>275</v>
       </c>
-      <c r="D83" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>276</v>
-      </c>
       <c r="F83" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H83" s="6"/>
       <c r="I83" s="8"/>
@@ -4353,25 +4357,25 @@
     </row>
     <row r="84" spans="1:10" ht="32" customHeight="1">
       <c r="A84" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="B84" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C84" s="8" t="s">
+      <c r="D84" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" s="8" t="s">
         <v>278</v>
       </c>
-      <c r="D84" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E84" s="8" t="s">
-        <v>279</v>
-      </c>
       <c r="F84" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H84" s="6"/>
       <c r="I84" s="8"/>
@@ -4379,25 +4383,25 @@
     </row>
     <row r="85" spans="1:10" ht="32" customHeight="1">
       <c r="A85" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="B85" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C85" s="8" t="s">
+      <c r="D85" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E85" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="D85" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>282</v>
-      </c>
       <c r="F85" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H85" s="6"/>
       <c r="I85" s="8"/>
@@ -4405,25 +4409,25 @@
     </row>
     <row r="86" spans="1:10" ht="32" customHeight="1">
       <c r="A86" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="B86" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C86" s="8" t="s">
+      <c r="D86" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E86" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="D86" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="F86" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H86" s="6"/>
       <c r="I86" s="8"/>
@@ -4431,25 +4435,25 @@
     </row>
     <row r="87" spans="1:10" ht="32" customHeight="1">
       <c r="A87" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B87" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C87" s="8" t="s">
+      <c r="D87" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="8" t="s">
         <v>287</v>
       </c>
-      <c r="D87" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>288</v>
-      </c>
       <c r="F87" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H87" s="6"/>
       <c r="I87" s="8"/>
@@ -4457,25 +4461,25 @@
     </row>
     <row r="88" spans="1:10" ht="32" customHeight="1">
       <c r="A88" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="B88" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C88" s="8" t="s">
+      <c r="D88" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E88" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="D88" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>291</v>
-      </c>
       <c r="F88" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H88" s="6"/>
       <c r="I88" s="8"/>
@@ -4483,25 +4487,25 @@
     </row>
     <row r="89" spans="1:10" ht="32" customHeight="1">
       <c r="A89" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C89" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B89" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C89" s="8" t="s">
+      <c r="D89" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E89" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="D89" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>294</v>
-      </c>
       <c r="F89" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G89" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H89" s="6"/>
       <c r="I89" s="8"/>
@@ -4509,25 +4513,25 @@
     </row>
     <row r="90" spans="1:10" ht="32" customHeight="1">
       <c r="A90" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="B90" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C90" s="8" t="s">
+      <c r="D90" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E90" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="D90" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E90" s="8" t="s">
-        <v>297</v>
-      </c>
       <c r="F90" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H90" s="6"/>
       <c r="I90" s="8"/>
@@ -4535,443 +4539,443 @@
     </row>
     <row r="91" spans="1:10" ht="32" customHeight="1">
       <c r="A91" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="B91" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C91" s="8" t="s">
+      <c r="D91" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="D91" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E91" s="8" t="s">
+      <c r="F91" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I91" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="F91" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="I91" s="8" t="s">
+      <c r="J91" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="J91" s="8" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="32" customHeight="1">
       <c r="A92" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="B92" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C92" s="12" t="s">
+      <c r="D92" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E92" s="12" t="s">
         <v>304</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E92" s="12" t="s">
-        <v>305</v>
       </c>
       <c r="F92" s="13">
         <v>46170</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H92" s="10"/>
       <c r="I92" s="12"/>
       <c r="J92" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93" spans="1:10" ht="32" customHeight="1">
       <c r="A93" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" s="12" t="s">
         <v>306</v>
       </c>
-      <c r="B93" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C93" s="12" t="s">
+      <c r="D93" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E93" s="12" t="s">
         <v>307</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E93" s="12" t="s">
-        <v>308</v>
       </c>
       <c r="F93" s="13">
         <v>46170</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H93" s="10"/>
       <c r="I93" s="12"/>
       <c r="J93" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="32" customHeight="1">
       <c r="A94" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="8" t="s">
         <v>309</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E94" s="8" t="s">
-        <v>310</v>
       </c>
       <c r="F94" s="9">
         <v>46171.484722222223</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I94" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="J94" s="8" t="s">
         <v>311</v>
-      </c>
-      <c r="J94" s="8" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="32" customHeight="1">
       <c r="A95" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="B95" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C95" s="8" t="s">
+      <c r="D95" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="8" t="s">
         <v>314</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>315</v>
       </c>
       <c r="F95" s="9">
         <v>46171.479861111111</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J95" s="8"/>
     </row>
     <row r="96" spans="1:10" ht="32" customHeight="1">
       <c r="A96" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="B96" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C96" s="8" t="s">
+      <c r="D96" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E96" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E96" s="8" t="s">
-        <v>319</v>
       </c>
       <c r="F96" s="9">
         <v>46171.513888888891</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I96" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="J96" s="8" t="s">
         <v>320</v>
-      </c>
-      <c r="J96" s="8" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="32" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C97" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="D97" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E97" s="17" t="s">
         <v>322</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E97" s="17" t="s">
-        <v>323</v>
       </c>
       <c r="F97" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H97" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="J97" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:10" ht="32" customHeight="1">
       <c r="A98" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E98" s="8" t="s">
         <v>325</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E98" s="8" t="s">
-        <v>326</v>
       </c>
       <c r="F98" s="9">
         <v>46171.451388888891</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I98" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="J98" s="8" t="s">
         <v>327</v>
-      </c>
-      <c r="J98" s="8" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="99" spans="1:10" ht="32" customHeight="1">
       <c r="A99" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C99" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B99" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C99" s="12" t="s">
+      <c r="D99" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E99" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="D99" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E99" s="12" t="s">
+      <c r="F99" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="I99" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="F99" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H99" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="I99" s="12" t="s">
+      <c r="J99" s="12" t="s">
         <v>332</v>
-      </c>
-      <c r="J99" s="12" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="100" spans="1:10" ht="32" customHeight="1">
       <c r="A100" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C100" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B100" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C100" s="8" t="s">
+      <c r="D100" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E100" s="8" t="s">
         <v>335</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E100" s="8" t="s">
-        <v>336</v>
       </c>
       <c r="F100" s="9">
         <v>46171.513888888891</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J100" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="101" spans="1:10" ht="32" customHeight="1">
       <c r="A101" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C101" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="B101" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C101" s="8" t="s">
+      <c r="D101" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E101" s="8" t="s">
-        <v>340</v>
       </c>
       <c r="F101" s="9">
         <v>46171.477777777778</v>
       </c>
       <c r="G101" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I101" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="J101" s="8" t="s">
         <v>341</v>
-      </c>
-      <c r="J101" s="8" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="102" spans="1:10" ht="32" customHeight="1">
       <c r="A102" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="C102" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="B102" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C102" s="12" t="s">
+      <c r="D102" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="E102" s="12" t="s">
         <v>344</v>
-      </c>
-      <c r="D102" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="E102" s="12" t="s">
-        <v>345</v>
       </c>
       <c r="F102" s="13">
         <v>46171.477777777778</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H102" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I102" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="J102" s="12" t="s">
         <v>346</v>
-      </c>
-      <c r="J102" s="12" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="103" spans="1:10" ht="32" customHeight="1">
       <c r="A103" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="C103" s="8" t="s">
         <v>348</v>
       </c>
-      <c r="B103" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="C103" s="8" t="s">
+      <c r="D103" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="8" t="s">
         <v>349</v>
       </c>
-      <c r="D103" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E103" s="8" t="s">
-        <v>350</v>
-      </c>
       <c r="F103" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G103" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H103" s="6"/>
       <c r="I103" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J103" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="104" spans="1:10" ht="32" customHeight="1">
       <c r="A104" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E104" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="B104" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D104" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E104" s="8" t="s">
+      <c r="F104" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="G104" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I104" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="F104" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="G104" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I104" s="8" t="s">
+      <c r="J104" s="8" t="s">
         <v>354</v>
-      </c>
-      <c r="J104" s="8" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="105" spans="1:10" ht="26" customHeight="1">
       <c r="A105" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -4985,209 +4989,209 @@
     </row>
     <row r="106" spans="1:10" ht="32" customHeight="1">
       <c r="A106" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B106" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="C106" s="17" t="s">
         <v>358</v>
       </c>
-      <c r="C106" s="17" t="s">
+      <c r="D106" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E106" s="17" t="s">
         <v>359</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E106" s="17" t="s">
-        <v>360</v>
       </c>
       <c r="F106" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H106" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I106" s="17"/>
       <c r="J106" s="17" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:10" ht="32" customHeight="1">
       <c r="A107" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>362</v>
       </c>
-      <c r="B107" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C107" s="8" t="s">
+      <c r="D107" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E107" s="8" t="s">
         <v>363</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="8" t="s">
-        <v>364</v>
       </c>
       <c r="F107" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H107" s="6"/>
       <c r="I107" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J107" s="8"/>
     </row>
     <row r="108" spans="1:10" ht="32" customHeight="1">
       <c r="A108" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C108" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="B108" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C108" s="8" t="s">
+      <c r="D108" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" s="8" t="s">
         <v>367</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" s="8" t="s">
-        <v>368</v>
       </c>
       <c r="F108" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H108" s="6"/>
       <c r="I108" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J108" s="8"/>
     </row>
     <row r="109" spans="1:10" ht="32" customHeight="1">
       <c r="A109" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C109" s="8" t="s">
         <v>370</v>
       </c>
-      <c r="B109" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C109" s="8" t="s">
+      <c r="D109" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E109" s="8" t="s">
         <v>371</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>372</v>
       </c>
       <c r="F109" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H109" s="6"/>
       <c r="I109" s="8" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="J109" s="8"/>
     </row>
     <row r="110" spans="1:10" ht="32" customHeight="1">
       <c r="A110" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C110" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="B110" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C110" s="8" t="s">
+      <c r="D110" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E110" s="8" t="s">
         <v>374</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="8" t="s">
-        <v>375</v>
       </c>
       <c r="F110" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H110" s="6"/>
       <c r="I110" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="J110" s="8"/>
     </row>
     <row r="111" spans="1:10" ht="32" customHeight="1">
       <c r="A111" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C111" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="B111" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C111" s="8" t="s">
+      <c r="D111" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E111" s="8" t="s">
         <v>378</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E111" s="8" t="s">
-        <v>379</v>
       </c>
       <c r="F111" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H111" s="6"/>
       <c r="I111" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="J111" s="8"/>
     </row>
     <row r="112" spans="1:10" ht="32" customHeight="1">
       <c r="A112" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="B112" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="C112" s="22" t="s">
         <v>381</v>
       </c>
-      <c r="B112" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="C112" s="22" t="s">
+      <c r="D112" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" s="22" t="s">
         <v>382</v>
-      </c>
-      <c r="D112" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E112" s="22" t="s">
-        <v>383</v>
       </c>
       <c r="F112" s="23">
         <v>46175.777777777781</v>
       </c>
       <c r="G112" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H112" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I112" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="J112" s="22" t="s">
         <v>384</v>
-      </c>
-      <c r="J112" s="22" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="113" spans="1:10" ht="26" customHeight="1">
       <c r="A113" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -5201,89 +5205,89 @@
     </row>
     <row r="114" spans="1:10" ht="32" customHeight="1">
       <c r="A114" s="15" t="s">
+        <v>386</v>
+      </c>
+      <c r="B114" s="16" t="s">
         <v>387</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="C114" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="C114" s="17" t="s">
+      <c r="D114" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E114" s="17" t="s">
         <v>389</v>
-      </c>
-      <c r="D114" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E114" s="17" t="s">
-        <v>390</v>
       </c>
       <c r="F114" s="18">
         <v>46175.794444444444</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H114" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I114" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="J114" s="17" t="s">
         <v>391</v>
-      </c>
-      <c r="J114" s="17" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="115" spans="1:10" ht="32" customHeight="1">
       <c r="A115" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="B115" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="C115" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="B115" s="16" t="s">
-        <v>388</v>
-      </c>
-      <c r="C115" s="17" t="s">
+      <c r="D115" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E115" s="17" t="s">
         <v>394</v>
-      </c>
-      <c r="D115" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E115" s="17" t="s">
-        <v>395</v>
       </c>
       <c r="F115" s="18">
         <v>46175.794444444444</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H115" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I115" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="J115" s="17" t="s">
         <v>396</v>
-      </c>
-      <c r="J115" s="17" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="116" spans="1:10" ht="32" customHeight="1">
       <c r="A116" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C116" s="8" t="s">
         <v>398</v>
       </c>
-      <c r="B116" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C116" s="8" t="s">
+      <c r="D116" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E116" s="8" t="s">
         <v>399</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E116" s="8" t="s">
-        <v>400</v>
       </c>
       <c r="F116" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H116" s="6"/>
       <c r="I116" s="8"/>
@@ -5291,55 +5295,55 @@
     </row>
     <row r="117" spans="1:10" ht="32" customHeight="1">
       <c r="A117" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C117" s="8" t="s">
         <v>401</v>
       </c>
-      <c r="B117" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C117" s="8" t="s">
+      <c r="D117" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E117" s="8" t="s">
         <v>402</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E117" s="8" t="s">
-        <v>403</v>
       </c>
       <c r="F117" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J117" s="8"/>
     </row>
     <row r="118" spans="1:10" ht="32" customHeight="1">
       <c r="A118" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C118" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="B118" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C118" s="8" t="s">
+      <c r="D118" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E118" s="8" t="s">
         <v>406</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E118" s="8" t="s">
-        <v>407</v>
       </c>
       <c r="F118" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H118" s="6"/>
       <c r="I118" s="8"/>
@@ -5347,7 +5351,7 @@
     </row>
     <row r="119" spans="1:10" ht="26" customHeight="1">
       <c r="A119" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -5361,113 +5365,113 @@
     </row>
     <row r="120" spans="1:10" ht="32" customHeight="1">
       <c r="A120" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="B120" s="16" t="s">
         <v>409</v>
       </c>
-      <c r="B120" s="16" t="s">
+      <c r="C120" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="C120" s="17" t="s">
+      <c r="D120" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E120" s="17" t="s">
         <v>411</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E120" s="17" t="s">
-        <v>412</v>
       </c>
       <c r="F120" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H120" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I120" s="17" t="s">
+        <v>412</v>
+      </c>
+      <c r="J120" s="17" t="s">
         <v>413</v>
-      </c>
-      <c r="J120" s="17" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="121" spans="1:10" ht="32" customHeight="1">
       <c r="A121" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C121" s="8" t="s">
         <v>415</v>
       </c>
-      <c r="B121" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="C121" s="8" t="s">
+      <c r="D121" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E121" s="8" t="s">
         <v>416</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E121" s="8" t="s">
-        <v>417</v>
       </c>
       <c r="F121" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G121" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H121" s="6"/>
       <c r="I121" s="8" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J121" s="8"/>
     </row>
     <row r="122" spans="1:10" ht="32" customHeight="1">
       <c r="A122" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C122" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="B122" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="C122" s="8" t="s">
+      <c r="D122" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E122" s="8" t="s">
         <v>420</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E122" s="8" t="s">
-        <v>421</v>
       </c>
       <c r="F122" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H122" s="6"/>
       <c r="I122" s="8" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J122" s="8"/>
     </row>
     <row r="123" spans="1:10" ht="32" customHeight="1">
       <c r="A123" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C123" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="B123" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="C123" s="8" t="s">
+      <c r="D123" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E123" s="8" t="s">
         <v>424</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E123" s="8" t="s">
-        <v>425</v>
       </c>
       <c r="F123" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G123" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H123" s="6"/>
       <c r="I123" s="8"/>
@@ -5475,57 +5479,57 @@
     </row>
     <row r="124" spans="1:10" ht="32" customHeight="1">
       <c r="A124" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="B124" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="C124" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="C124" s="17" t="s">
+      <c r="D124" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E124" s="17" t="s">
         <v>427</v>
-      </c>
-      <c r="D124" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E124" s="17" t="s">
-        <v>428</v>
       </c>
       <c r="F124" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H124" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I124" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="J124" s="17" t="s">
         <v>429</v>
-      </c>
-      <c r="J124" s="17" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="125" spans="1:10" ht="32" customHeight="1">
       <c r="A125" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C125" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="B125" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="C125" s="8" t="s">
+      <c r="D125" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E125" s="8" t="s">
         <v>432</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E125" s="8" t="s">
-        <v>433</v>
       </c>
       <c r="F125" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G125" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H125" s="6"/>
       <c r="I125" s="8"/>
@@ -5533,7 +5537,7 @@
     </row>
     <row r="126" spans="1:10" ht="26" customHeight="1">
       <c r="A126" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5547,53 +5551,53 @@
     </row>
     <row r="127" spans="1:10" ht="32" customHeight="1">
       <c r="A127" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="B127" s="16" t="s">
         <v>435</v>
       </c>
-      <c r="B127" s="16" t="s">
+      <c r="C127" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="C127" s="17" t="s">
+      <c r="D127" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E127" s="17" t="s">
         <v>437</v>
-      </c>
-      <c r="D127" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E127" s="17" t="s">
-        <v>438</v>
       </c>
       <c r="F127" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G127" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H127" s="15"/>
       <c r="I127" s="17"/>
       <c r="J127" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="128" spans="1:10" ht="32" customHeight="1">
       <c r="A128" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C128" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="B128" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C128" s="8" t="s">
+      <c r="D128" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E128" s="8" t="s">
         <v>441</v>
-      </c>
-      <c r="D128" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>442</v>
       </c>
       <c r="F128" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H128" s="6"/>
       <c r="I128" s="8"/>
@@ -5601,25 +5605,25 @@
     </row>
     <row r="129" spans="1:10" ht="32" customHeight="1">
       <c r="A129" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C129" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="B129" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C129" s="8" t="s">
+      <c r="D129" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E129" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="D129" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="F129" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G129" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H129" s="6"/>
       <c r="I129" s="8"/>
@@ -5627,25 +5631,25 @@
     </row>
     <row r="130" spans="1:10" ht="32" customHeight="1">
       <c r="A130" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C130" s="8" t="s">
         <v>446</v>
       </c>
-      <c r="B130" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C130" s="8" t="s">
+      <c r="D130" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E130" s="8" t="s">
         <v>447</v>
-      </c>
-      <c r="D130" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E130" s="8" t="s">
-        <v>448</v>
       </c>
       <c r="F130" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H130" s="6"/>
       <c r="I130" s="8"/>
@@ -5653,57 +5657,57 @@
     </row>
     <row r="131" spans="1:10" ht="32" customHeight="1">
       <c r="A131" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C131" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="B131" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>450</v>
-      </c>
       <c r="D131" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E131" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="F131" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I131" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="J131" s="8" t="s">
         <v>451</v>
-      </c>
-      <c r="J131" s="8" t="s">
-        <v>452</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="32" customHeight="1">
       <c r="A132" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C132" s="8" t="s">
         <v>453</v>
       </c>
-      <c r="B132" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C132" s="8" t="s">
+      <c r="D132" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E132" s="8" t="s">
         <v>454</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>455</v>
       </c>
       <c r="F132" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H132" s="6"/>
       <c r="I132" s="8"/>
@@ -5711,25 +5715,25 @@
     </row>
     <row r="133" spans="1:10" ht="32" customHeight="1">
       <c r="A133" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C133" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="B133" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="C133" s="8" t="s">
+      <c r="D133" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E133" s="8" t="s">
         <v>457</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E133" s="8" t="s">
-        <v>458</v>
       </c>
       <c r="F133" s="14">
         <v>46175.690972222219</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H133" s="6"/>
       <c r="I133" s="8"/>
@@ -5737,270 +5741,270 @@
     </row>
     <row r="134" spans="1:10" ht="32" customHeight="1">
       <c r="A134" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="B134" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="C134" s="17" t="s">
+        <v>436</v>
+      </c>
+      <c r="D134" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134" s="17" t="s">
         <v>459</v>
-      </c>
-      <c r="B134" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="C134" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="D134" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="E134" s="17" t="s">
-        <v>460</v>
       </c>
       <c r="F134" s="18">
         <v>46175.746527777781</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H134" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I134" s="17" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J134" s="17" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="32" customHeight="1">
       <c r="A135" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="B135" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="C135" s="22" t="s">
         <v>462</v>
-      </c>
-      <c r="B135" s="21" t="s">
-        <v>436</v>
-      </c>
-      <c r="C135" s="22" t="s">
-        <v>463</v>
       </c>
       <c r="D135" s="20"/>
       <c r="E135" s="22" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F135" s="23">
         <v>46175.777777777781</v>
       </c>
       <c r="G135" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H135" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I135" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="J135" s="22" t="s">
         <v>465</v>
-      </c>
-      <c r="J135" s="22" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="32" customHeight="1">
       <c r="A136" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="B136" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="B136" s="21" t="s">
+      <c r="C136" s="22" t="s">
         <v>468</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>469</v>
       </c>
       <c r="D136" s="20"/>
       <c r="E136" s="22" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F136" s="23">
         <v>46175.794444444444</v>
       </c>
       <c r="G136" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H136" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I136" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="J136" s="22" t="s">
         <v>471</v>
-      </c>
-      <c r="J136" s="22" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="32" customHeight="1">
       <c r="A137" s="20" t="s">
+        <v>472</v>
+      </c>
+      <c r="B137" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="C137" s="22" t="s">
         <v>473</v>
-      </c>
-      <c r="B137" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="C137" s="22" t="s">
-        <v>474</v>
       </c>
       <c r="D137" s="20"/>
       <c r="E137" s="22" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F137" s="23">
         <v>46175.777777777781</v>
       </c>
       <c r="G137" s="26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H137" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I137" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="J137" s="22" t="s">
         <v>476</v>
-      </c>
-      <c r="J137" s="22" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="32" customHeight="1">
       <c r="A138" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="B138" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="B138" s="5" t="s">
+      <c r="C138" s="24" t="s">
         <v>479</v>
-      </c>
-      <c r="C138" s="24" t="s">
-        <v>480</v>
       </c>
       <c r="D138" s="25"/>
       <c r="E138" s="24" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F138" s="23">
         <v>46175.777777777781</v>
       </c>
       <c r="G138" s="26" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H138" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I138" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="J138" s="24" t="s">
         <v>482</v>
-      </c>
-      <c r="J138" s="24" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="139" spans="1:10" ht="32" customHeight="1">
       <c r="A139" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="C139" s="8" t="s">
         <v>484</v>
-      </c>
-      <c r="B139" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>485</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F139" s="18">
         <v>46175.777777777781</v>
       </c>
       <c r="G139" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H139" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J139" s="8"/>
     </row>
     <row r="140" spans="1:10" ht="32" customHeight="1">
       <c r="A140" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="C140" s="8" t="s">
         <v>487</v>
-      </c>
-      <c r="B140" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>488</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F140" s="18">
         <v>46175.818749999999</v>
       </c>
-      <c r="G140" s="32" t="s">
-        <v>21</v>
+      <c r="G140" s="27" t="s">
+        <v>20</v>
       </c>
       <c r="H140" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J140" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="141" spans="1:10" ht="32" customHeight="1">
       <c r="A141" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="B141" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="B141" s="7" t="s">
+      <c r="C141" s="8" t="s">
         <v>492</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>493</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F141" s="18">
         <v>46175.818749999999</v>
       </c>
-      <c r="G141" s="32" t="s">
-        <v>21</v>
+      <c r="G141" s="27" t="s">
+        <v>20</v>
       </c>
       <c r="H141" s="15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J141" s="8" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="32" customHeight="1">
       <c r="A142" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="C142" s="8" t="s">
         <v>496</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>497</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F142" s="18">
         <v>46175.794444444444</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H142" s="15" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I142" s="8"/>
       <c r="J142" s="8" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
